--- a/SeleniumTests/TestDataFolder/CustomerTestDataValid.xlsx
+++ b/SeleniumTests/TestDataFolder/CustomerTestDataValid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B407A722-6519-46B0-80CC-6B12BD68FABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7F1117-3F63-48D3-9607-2E853FFCE7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateCustomerTestData" sheetId="1" r:id="rId1"/>
@@ -54,15 +54,9 @@
     <t>Lorong 333, Taman 444</t>
   </si>
   <si>
-    <t>searchText</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
-    <t>category</t>
-  </si>
-  <si>
     <t>ALL</t>
   </si>
   <si>
@@ -72,51 +66,6 @@
     <t>INACTIVE</t>
   </si>
   <si>
-    <t>Custname</t>
-  </si>
-  <si>
-    <t>CustTinNumber</t>
-  </si>
-  <si>
-    <t>BEregisterType</t>
-  </si>
-  <si>
-    <t>CustRegisterID</t>
-  </si>
-  <si>
-    <t>Custsst</t>
-  </si>
-  <si>
-    <t>CustEmail</t>
-  </si>
-  <si>
-    <t>CustContactNumber</t>
-  </si>
-  <si>
-    <t>CustCity</t>
-  </si>
-  <si>
-    <t>CustState</t>
-  </si>
-  <si>
-    <t>CustPosCode</t>
-  </si>
-  <si>
-    <t>CustCountry</t>
-  </si>
-  <si>
-    <t>CustAddress1</t>
-  </si>
-  <si>
-    <t>CustAddress2</t>
-  </si>
-  <si>
-    <t>CustAddress3</t>
-  </si>
-  <si>
-    <t>CustExternalCode</t>
-  </si>
-  <si>
     <t>BRN</t>
   </si>
   <si>
@@ -147,27 +96,15 @@
     <t>Success</t>
   </si>
   <si>
-    <t>CustomerCode</t>
-  </si>
-  <si>
-    <t>lhdnStatus</t>
-  </si>
-  <si>
     <t>Pending</t>
   </si>
   <si>
     <t>Failed</t>
   </si>
   <si>
-    <t>columnIndex</t>
-  </si>
-  <si>
     <t>CUST_000004</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Inactive</t>
   </si>
   <si>
@@ -187,6 +124,69 @@
   </si>
   <si>
     <t>202001038405</t>
+  </si>
+  <si>
+    <t>Customer Name</t>
+  </si>
+  <si>
+    <t>Customer Tin Number</t>
+  </si>
+  <si>
+    <t>Customer Register Type</t>
+  </si>
+  <si>
+    <t>Customer Register ID</t>
+  </si>
+  <si>
+    <t>Customer SST</t>
+  </si>
+  <si>
+    <t>Customer Email</t>
+  </si>
+  <si>
+    <t>Customer Contact Number</t>
+  </si>
+  <si>
+    <t>Customer City</t>
+  </si>
+  <si>
+    <t>Customer State</t>
+  </si>
+  <si>
+    <t>Customer Pos Code</t>
+  </si>
+  <si>
+    <t>Customer Country</t>
+  </si>
+  <si>
+    <t>Customer Address1</t>
+  </si>
+  <si>
+    <t>Customer Address2</t>
+  </si>
+  <si>
+    <t>Customer Address3</t>
+  </si>
+  <si>
+    <t>Customer External Code</t>
+  </si>
+  <si>
+    <t>Search Text</t>
+  </si>
+  <si>
+    <t>Refer Column Index</t>
+  </si>
+  <si>
+    <t>Customer Code</t>
+  </si>
+  <si>
+    <t>Customer Status (Active/Inactive)</t>
+  </si>
+  <si>
+    <t>Customer Category (ALL/ACTIVE/INACTIVE)</t>
+  </si>
+  <si>
+    <t>LHDN Status (Pending/Success/Failed)</t>
   </si>
 </sst>
 </file>
@@ -522,85 +522,86 @@
   <cols>
     <col min="4" max="4" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="1"/>
+    <col min="16" max="16" width="30.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="L1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="M1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="N1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="O1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="P1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>12345</v>
@@ -615,10 +616,10 @@
         <v>3</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="P2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -635,20 +636,21 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="20.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -656,7 +658,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -664,7 +666,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -672,7 +674,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -680,7 +682,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -688,7 +690,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -706,90 +708,109 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C5B1C65-19F6-40A2-B045-F22D83E84636}">
   <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="30.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
       <c r="J1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="L1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="M1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="N1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="O1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="P1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="Q1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K2">
         <v>12345</v>
@@ -804,13 +825,13 @@
         <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="P2" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -825,25 +846,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CF168F-C049-4DB3-BB94-989C9CCF7787}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="38.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -855,25 +879,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4940570E-6620-468A-A427-96A8B9A10525}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
